--- a/成本卡1.16.xlsx
+++ b/成本卡1.16.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="14860"/>
+    <workbookView windowHeight="14660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -129,9 +129,6 @@
     <t>吮指猪蹄</t>
   </si>
   <si>
-    <t>薯条</t>
-  </si>
-  <si>
     <t>手撕包菜</t>
   </si>
   <si>
@@ -162,9 +159,6 @@
     <t>柠檬酸菜鱼（大份）</t>
   </si>
   <si>
-    <t>蜜汁鸡翅</t>
-  </si>
-  <si>
     <t>秘制蟹（小份）</t>
   </si>
   <si>
@@ -259,6 +253,12 @@
   </si>
   <si>
     <t>100元代金券</t>
+  </si>
+  <si>
+    <t>静小静儿童餐三次卡</t>
+  </si>
+  <si>
+    <t>有效期三个月</t>
   </si>
 </sst>
 </file>
@@ -920,7 +920,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -943,18 +943,7 @@
     <xf numFmtId="10" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="3" applyBorder="1">
@@ -1274,14 +1263,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D62"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" outlineLevelCol="3"/>
+  <dimension ref="A1:E61"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="26.2788461538462" style="1" customWidth="1"/>
     <col min="2" max="2" width="12" style="2" customWidth="1"/>
     <col min="3" max="3" width="14.5" style="2" customWidth="1"/>
     <col min="4" max="4" width="17.625" style="2" customWidth="1"/>
-    <col min="5" max="16384" width="9" style="2"/>
+    <col min="5" max="5" width="20.6634615384615" style="2" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -1309,7 +1299,7 @@
         <v>54</v>
       </c>
       <c r="D2" s="7">
-        <f>(B2-C2)/B2</f>
+        <f t="shared" ref="D2:D28" si="0">(B2-C2)/B2</f>
         <v>0.485714285714286</v>
       </c>
     </row>
@@ -1324,7 +1314,7 @@
         <v>79.5</v>
       </c>
       <c r="D3" s="7">
-        <f>(B3-C3)/B3</f>
+        <f t="shared" si="0"/>
         <v>0.598484848484849</v>
       </c>
     </row>
@@ -1339,7 +1329,7 @@
         <v>19.5</v>
       </c>
       <c r="D4" s="7">
-        <f>(B4-C4)/B4</f>
+        <f t="shared" si="0"/>
         <v>0.713235294117647</v>
       </c>
     </row>
@@ -1354,7 +1344,7 @@
         <v>6</v>
       </c>
       <c r="D5" s="7">
-        <f>(B5-C5)/B5</f>
+        <f t="shared" si="0"/>
         <v>0.666666666666667</v>
       </c>
     </row>
@@ -1369,12 +1359,12 @@
         <v>1</v>
       </c>
       <c r="D6" s="7">
-        <f>(B6-C6)/B6</f>
+        <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="3" t="s">
         <v>9</v>
       </c>
       <c r="B7" s="6">
@@ -1384,12 +1374,12 @@
         <v>28.5</v>
       </c>
       <c r="D7" s="7">
-        <f>(B7-C7)/B7</f>
+        <f t="shared" si="0"/>
         <v>0.540322580645161</v>
       </c>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="3" t="s">
         <v>10</v>
       </c>
       <c r="B8" s="6">
@@ -1399,7 +1389,7 @@
         <v>42.5</v>
       </c>
       <c r="D8" s="7">
-        <f>(B8-C8)/B8</f>
+        <f t="shared" si="0"/>
         <v>0.527777777777778</v>
       </c>
     </row>
@@ -1414,7 +1404,7 @@
         <v>14.5</v>
       </c>
       <c r="D9" s="7">
-        <f>(B9-C9)/B9</f>
+        <f t="shared" si="0"/>
         <v>0.618421052631579</v>
       </c>
     </row>
@@ -1429,7 +1419,7 @@
         <v>19.8</v>
       </c>
       <c r="D10" s="7">
-        <f>(B10-C10)/B10</f>
+        <f t="shared" si="0"/>
         <v>0.658620689655173</v>
       </c>
     </row>
@@ -1444,7 +1434,7 @@
         <v>32</v>
       </c>
       <c r="D11" s="7">
-        <f>(B11-C11)/B11</f>
+        <f t="shared" si="0"/>
         <v>0.529411764705882</v>
       </c>
     </row>
@@ -1459,7 +1449,7 @@
         <v>18.05</v>
       </c>
       <c r="D12" s="7">
-        <f>(B12-C12)/B12</f>
+        <f t="shared" si="0"/>
         <v>0.734558823529412</v>
       </c>
     </row>
@@ -1474,7 +1464,7 @@
         <v>21.75</v>
       </c>
       <c r="D13" s="7">
-        <f>(B13-C13)/B13</f>
+        <f t="shared" si="0"/>
         <v>0.556122448979592</v>
       </c>
     </row>
@@ -1489,7 +1479,7 @@
         <v>43.15</v>
       </c>
       <c r="D14" s="7">
-        <f>(B14-C14)/B14</f>
+        <f t="shared" si="0"/>
         <v>0.520555555555556</v>
       </c>
     </row>
@@ -1504,7 +1494,7 @@
         <v>8.35</v>
       </c>
       <c r="D15" s="7">
-        <f>(B15-C15)/B15</f>
+        <f t="shared" si="0"/>
         <v>0.478125</v>
       </c>
     </row>
@@ -1519,7 +1509,7 @@
         <v>14.45</v>
       </c>
       <c r="D16" s="7">
-        <f>(B16-C16)/B16</f>
+        <f t="shared" si="0"/>
         <v>0.343181818181818</v>
       </c>
     </row>
@@ -1534,7 +1524,7 @@
         <v>19.55</v>
       </c>
       <c r="D17" s="7">
-        <f>(B17-C17)/B17</f>
+        <f t="shared" si="0"/>
         <v>0.592708333333333</v>
       </c>
     </row>
@@ -1549,19 +1539,19 @@
         <v>29.8</v>
       </c>
       <c r="D18" s="7">
-        <f>(B18-C18)/B18</f>
+        <f t="shared" si="0"/>
         <v>0.561764705882353</v>
       </c>
     </row>
     <row r="19" spans="1:4">
-      <c r="A19" s="8" t="s">
+      <c r="A19" s="5" t="s">
         <v>21</v>
       </c>
       <c r="B19" s="6">
-        <v>11.9</v>
+        <v>22</v>
       </c>
       <c r="C19" s="6">
-        <v>3.57</v>
+        <v>6.6</v>
       </c>
       <c r="D19" s="7">
         <f>(B19-C19)/B19</f>
@@ -1573,14 +1563,14 @@
         <v>22</v>
       </c>
       <c r="B20" s="6">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="C20" s="6">
-        <v>6.6</v>
+        <v>14.75</v>
       </c>
       <c r="D20" s="7">
         <f>(B20-C20)/B20</f>
-        <v>0.7</v>
+        <v>0.745689655172414</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -1588,14 +1578,14 @@
         <v>23</v>
       </c>
       <c r="B21" s="6">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="C21" s="6">
-        <v>14.75</v>
+        <v>27.5</v>
       </c>
       <c r="D21" s="7">
         <f>(B21-C21)/B21</f>
-        <v>0.745689655172414</v>
+        <v>0.595588235294118</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -1603,14 +1593,14 @@
         <v>24</v>
       </c>
       <c r="B22" s="6">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="C22" s="6">
-        <v>27.5</v>
+        <v>13.85</v>
       </c>
       <c r="D22" s="7">
         <f>(B22-C22)/B22</f>
-        <v>0.595588235294118</v>
+        <v>0.761206896551724</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -1618,44 +1608,44 @@
         <v>25</v>
       </c>
       <c r="B23" s="6">
-        <v>58</v>
+        <v>3</v>
       </c>
       <c r="C23" s="6">
-        <v>13.85</v>
+        <v>1</v>
       </c>
       <c r="D23" s="7">
         <f>(B23-C23)/B23</f>
-        <v>0.761206896551724</v>
+        <v>0.666666666666667</v>
       </c>
     </row>
     <row r="24" spans="1:4">
-      <c r="A24" s="5" t="s">
+      <c r="A24" s="3" t="s">
         <v>26</v>
       </c>
       <c r="B24" s="6">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="C24" s="6">
-        <v>1</v>
+        <v>12.39</v>
       </c>
       <c r="D24" s="7">
         <f>(B24-C24)/B24</f>
-        <v>0.666666666666667</v>
+        <v>0.572758620689655</v>
       </c>
     </row>
     <row r="25" spans="1:4">
-      <c r="A25" s="8" t="s">
+      <c r="A25" s="3" t="s">
         <v>27</v>
       </c>
       <c r="B25" s="6">
-        <v>29</v>
+        <v>105</v>
       </c>
       <c r="C25" s="6">
-        <v>12.39</v>
+        <v>45.5</v>
       </c>
       <c r="D25" s="7">
         <f>(B25-C25)/B25</f>
-        <v>0.572758620689655</v>
+        <v>0.566666666666667</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -1663,14 +1653,14 @@
         <v>28</v>
       </c>
       <c r="B26" s="6">
-        <v>105</v>
+        <v>198</v>
       </c>
       <c r="C26" s="6">
-        <v>45.5</v>
+        <v>78</v>
       </c>
       <c r="D26" s="7">
         <f>(B26-C26)/B26</f>
-        <v>0.566666666666667</v>
+        <v>0.606060606060606</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -1678,89 +1668,89 @@
         <v>29</v>
       </c>
       <c r="B27" s="6">
-        <v>198</v>
+        <v>48</v>
       </c>
       <c r="C27" s="6">
-        <v>78</v>
+        <v>25.5</v>
       </c>
       <c r="D27" s="7">
         <f>(B27-C27)/B27</f>
-        <v>0.606060606060606</v>
+        <v>0.46875</v>
       </c>
     </row>
     <row r="28" spans="1:4">
-      <c r="A28" s="8" t="s">
+      <c r="A28" s="5" t="s">
         <v>30</v>
       </c>
       <c r="B28" s="6">
-        <v>48</v>
+        <v>90</v>
       </c>
       <c r="C28" s="6">
-        <v>25.5</v>
+        <v>38.5</v>
       </c>
       <c r="D28" s="7">
         <f>(B28-C28)/B28</f>
-        <v>0.46875</v>
+        <v>0.572222222222222</v>
       </c>
     </row>
     <row r="29" spans="1:4">
-      <c r="A29" s="9" t="s">
+      <c r="A29" s="3" t="s">
         <v>31</v>
       </c>
       <c r="B29" s="6">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="C29" s="6">
-        <v>38.5</v>
+        <v>41.5</v>
       </c>
       <c r="D29" s="7">
-        <f t="shared" ref="D29:D34" si="0">(B29-C29)/B29</f>
-        <v>0.572222222222222</v>
+        <f t="shared" ref="D29:D42" si="1">(B29-C29)/B29</f>
+        <v>0.604761904761905</v>
       </c>
     </row>
     <row r="30" spans="1:4">
-      <c r="A30" s="8" t="s">
+      <c r="A30" s="3" t="s">
         <v>32</v>
       </c>
       <c r="B30" s="6">
-        <v>29</v>
+        <v>198</v>
       </c>
       <c r="C30" s="6">
-        <v>11.6</v>
+        <v>83</v>
       </c>
       <c r="D30" s="7">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
+        <f t="shared" si="1"/>
+        <v>0.580808080808081</v>
       </c>
     </row>
     <row r="31" spans="1:4">
-      <c r="A31" s="3" t="s">
+      <c r="A31" s="5" t="s">
         <v>33</v>
       </c>
       <c r="B31" s="6">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C31" s="6">
-        <v>41.5</v>
+        <v>42.95</v>
       </c>
       <c r="D31" s="7">
-        <f t="shared" si="0"/>
-        <v>0.604761904761905</v>
+        <f t="shared" si="1"/>
+        <v>0.602314814814815</v>
       </c>
     </row>
     <row r="32" spans="1:4">
-      <c r="A32" s="3" t="s">
+      <c r="A32" s="5" t="s">
         <v>34</v>
       </c>
       <c r="B32" s="6">
-        <v>198</v>
+        <v>68</v>
       </c>
       <c r="C32" s="6">
-        <v>83</v>
+        <v>24.5</v>
       </c>
       <c r="D32" s="7">
-        <f t="shared" si="0"/>
-        <v>0.580808080808081</v>
+        <f t="shared" si="1"/>
+        <v>0.639705882352941</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -1768,29 +1758,29 @@
         <v>35</v>
       </c>
       <c r="B33" s="6">
-        <v>108</v>
+        <v>56</v>
       </c>
       <c r="C33" s="6">
-        <v>42.95</v>
+        <v>22.8</v>
       </c>
       <c r="D33" s="7">
-        <f t="shared" si="0"/>
-        <v>0.602314814814815</v>
+        <f t="shared" si="1"/>
+        <v>0.592857142857143</v>
       </c>
     </row>
     <row r="34" spans="1:4">
-      <c r="A34" s="10" t="s">
+      <c r="A34" s="5" t="s">
         <v>36</v>
       </c>
       <c r="B34" s="6">
-        <v>68</v>
+        <v>48</v>
       </c>
       <c r="C34" s="6">
-        <v>24.5</v>
+        <v>14.65</v>
       </c>
       <c r="D34" s="7">
-        <f t="shared" si="0"/>
-        <v>0.639705882352941</v>
+        <f t="shared" si="1"/>
+        <v>0.694791666666667</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -1798,14 +1788,14 @@
         <v>37</v>
       </c>
       <c r="B35" s="6">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="C35" s="6">
-        <v>22.8</v>
+        <v>25</v>
       </c>
       <c r="D35" s="7">
-        <f>(B35-C35)/B35</f>
-        <v>0.592857142857143</v>
+        <f t="shared" si="1"/>
+        <v>0.67948717948718</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -1813,14 +1803,14 @@
         <v>38</v>
       </c>
       <c r="B36" s="6">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="C36" s="6">
-        <v>14.65</v>
+        <v>14.85</v>
       </c>
       <c r="D36" s="7">
-        <f>(B36-C36)/B36</f>
-        <v>0.694791666666667</v>
+        <f t="shared" si="1"/>
+        <v>0.609210526315789</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -1828,29 +1818,29 @@
         <v>39</v>
       </c>
       <c r="B37" s="6">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="C37" s="6">
-        <v>25</v>
+        <v>22.8</v>
       </c>
       <c r="D37" s="7">
-        <f>(B37-C37)/B37</f>
-        <v>0.67948717948718</v>
+        <f t="shared" si="1"/>
+        <v>0.606896551724138</v>
       </c>
     </row>
     <row r="38" spans="1:4">
-      <c r="A38" s="5" t="s">
+      <c r="A38" s="3" t="s">
         <v>40</v>
       </c>
       <c r="B38" s="6">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="C38" s="6">
-        <v>14.85</v>
+        <v>7.355</v>
       </c>
       <c r="D38" s="7">
-        <f>(B38-C38)/B38</f>
-        <v>0.609210526315789</v>
+        <f t="shared" si="1"/>
+        <v>0.665681818181818</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -1858,29 +1848,29 @@
         <v>41</v>
       </c>
       <c r="B39" s="6">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="C39" s="6">
-        <v>22.8</v>
+        <v>21.8</v>
       </c>
       <c r="D39" s="7">
-        <f>(B39-C39)/B39</f>
-        <v>0.606896551724138</v>
+        <f t="shared" si="1"/>
+        <v>0.679411764705882</v>
       </c>
     </row>
     <row r="40" spans="1:4">
-      <c r="A40" s="8" t="s">
+      <c r="A40" s="3" t="s">
         <v>42</v>
       </c>
       <c r="B40" s="6">
-        <v>22</v>
+        <v>62</v>
       </c>
       <c r="C40" s="6">
-        <v>7.355</v>
+        <v>25.5</v>
       </c>
       <c r="D40" s="7">
-        <f>(B40-C40)/B40</f>
-        <v>0.665681818181818</v>
+        <f t="shared" si="1"/>
+        <v>0.588709677419355</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -1888,44 +1878,43 @@
         <v>43</v>
       </c>
       <c r="B41" s="6">
-        <v>68</v>
+        <v>90</v>
       </c>
       <c r="C41" s="6">
-        <v>21.8</v>
+        <v>39.5</v>
       </c>
       <c r="D41" s="7">
-        <f>(B41-C41)/B41</f>
-        <v>0.679411764705882</v>
+        <f t="shared" si="1"/>
+        <v>0.561111111111111</v>
       </c>
     </row>
     <row r="42" spans="1:4">
-      <c r="A42" s="3" t="s">
+      <c r="A42" s="5" t="s">
         <v>44</v>
       </c>
       <c r="B42" s="6">
-        <v>62</v>
-      </c>
-      <c r="C42" s="6">
-        <v>25.5</v>
+        <v>98</v>
+      </c>
+      <c r="C42" s="8">
+        <v>41.8</v>
       </c>
       <c r="D42" s="7">
-        <f>(B42-C42)/B42</f>
-        <v>0.588709677419355</v>
+        <f t="shared" si="1"/>
+        <v>0.573469387755102</v>
       </c>
     </row>
     <row r="43" spans="1:4">
-      <c r="A43" s="9" t="s">
+      <c r="A43" s="5" t="s">
         <v>45</v>
       </c>
       <c r="B43" s="6">
-        <v>90</v>
-      </c>
-      <c r="C43" s="6">
-        <v>39.5</v>
+        <v>78</v>
+      </c>
+      <c r="C43" s="8">
+        <v>35.77</v>
       </c>
       <c r="D43" s="7">
-        <f>(B43-C43)/B43</f>
-        <v>0.561111111111111</v>
+        <v>0.541410256410256</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -1933,14 +1922,14 @@
         <v>46</v>
       </c>
       <c r="B44" s="6">
-        <v>98</v>
-      </c>
-      <c r="C44" s="11">
-        <v>41.8</v>
+        <v>15</v>
+      </c>
+      <c r="C44" s="6">
+        <v>6.85</v>
       </c>
       <c r="D44" s="7">
-        <f>(B44-C44)/B44</f>
-        <v>0.573469387755102</v>
+        <f t="shared" ref="D44:D58" si="2">(B44-C44)/B44</f>
+        <v>0.543333333333333</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -1948,13 +1937,14 @@
         <v>47</v>
       </c>
       <c r="B45" s="6">
-        <v>78</v>
-      </c>
-      <c r="C45" s="11">
-        <v>35.77</v>
+        <v>32</v>
+      </c>
+      <c r="C45" s="6">
+        <v>14.5</v>
       </c>
       <c r="D45" s="7">
-        <v>0.541410256410256</v>
+        <f t="shared" si="2"/>
+        <v>0.546875</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -1962,14 +1952,14 @@
         <v>48</v>
       </c>
       <c r="B46" s="6">
-        <v>15</v>
+        <v>78</v>
       </c>
       <c r="C46" s="6">
-        <v>6.85</v>
+        <v>36.8</v>
       </c>
       <c r="D46" s="7">
-        <f>(B46-C46)/B46</f>
-        <v>0.543333333333333</v>
+        <f t="shared" si="2"/>
+        <v>0.528205128205128</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -1977,29 +1967,29 @@
         <v>49</v>
       </c>
       <c r="B47" s="6">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="C47" s="6">
-        <v>14.5</v>
+        <v>23.5</v>
       </c>
       <c r="D47" s="7">
-        <f>(B47-C47)/B47</f>
-        <v>0.546875</v>
+        <f t="shared" si="2"/>
+        <v>0.580357142857143</v>
       </c>
     </row>
     <row r="48" spans="1:4">
-      <c r="A48" s="5" t="s">
+      <c r="A48" s="3" t="s">
         <v>50</v>
       </c>
       <c r="B48" s="6">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="C48" s="6">
-        <v>36.8</v>
+        <v>25.78</v>
       </c>
       <c r="D48" s="7">
-        <f>(B48-C48)/B48</f>
-        <v>0.528205128205128</v>
+        <f t="shared" si="2"/>
+        <v>0.584193548387097</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2007,44 +1997,44 @@
         <v>51</v>
       </c>
       <c r="B49" s="6">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="C49" s="6">
-        <v>23.5</v>
+        <v>16.5</v>
       </c>
       <c r="D49" s="7">
-        <f>(B49-C49)/B49</f>
-        <v>0.580357142857143</v>
+        <f t="shared" si="2"/>
+        <v>0.607142857142857</v>
       </c>
     </row>
     <row r="50" spans="1:4">
-      <c r="A50" s="8" t="s">
+      <c r="A50" s="5" t="s">
         <v>52</v>
       </c>
       <c r="B50" s="6">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="C50" s="6">
-        <v>25.78</v>
+        <v>25</v>
       </c>
       <c r="D50" s="7">
-        <f>(B50-C50)/B50</f>
-        <v>0.584193548387097</v>
+        <f t="shared" si="2"/>
+        <v>0.632352941176471</v>
       </c>
     </row>
     <row r="51" spans="1:4">
-      <c r="A51" s="5" t="s">
+      <c r="A51" s="3" t="s">
         <v>53</v>
       </c>
       <c r="B51" s="6">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="C51" s="6">
-        <v>16.5</v>
+        <v>11.69</v>
       </c>
       <c r="D51" s="7">
-        <f>(B51-C51)/B51</f>
-        <v>0.607142857142857</v>
+        <f t="shared" si="2"/>
+        <v>0.350555555555556</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2052,44 +2042,44 @@
         <v>54</v>
       </c>
       <c r="B52" s="6">
-        <v>68</v>
+        <v>48</v>
       </c>
       <c r="C52" s="6">
-        <v>25</v>
+        <v>22.5</v>
       </c>
       <c r="D52" s="7">
-        <f>(B52-C52)/B52</f>
-        <v>0.632352941176471</v>
+        <f t="shared" si="2"/>
+        <v>0.53125</v>
       </c>
     </row>
     <row r="53" spans="1:4">
-      <c r="A53" s="8" t="s">
+      <c r="A53" s="5" t="s">
         <v>55</v>
       </c>
       <c r="B53" s="6">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C53" s="6">
-        <v>11.69</v>
+        <v>8.5</v>
       </c>
       <c r="D53" s="7">
-        <f>(B53-C53)/B53</f>
-        <v>0.350555555555556</v>
+        <f t="shared" si="2"/>
+        <v>0.613636363636364</v>
       </c>
     </row>
     <row r="54" spans="1:4">
-      <c r="A54" s="5" t="s">
+      <c r="A54" s="3" t="s">
         <v>56</v>
       </c>
       <c r="B54" s="6">
-        <v>48</v>
+        <v>98</v>
       </c>
       <c r="C54" s="6">
-        <v>22.5</v>
+        <v>35.5</v>
       </c>
       <c r="D54" s="7">
-        <f>(B54-C54)/B54</f>
-        <v>0.53125</v>
+        <f t="shared" si="2"/>
+        <v>0.637755102040816</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2097,29 +2087,29 @@
         <v>57</v>
       </c>
       <c r="B55" s="6">
-        <v>22</v>
+        <v>168</v>
       </c>
       <c r="C55" s="6">
-        <v>8.5</v>
+        <v>74</v>
       </c>
       <c r="D55" s="7">
-        <f>(B55-C55)/B55</f>
-        <v>0.613636363636364</v>
+        <f t="shared" si="2"/>
+        <v>0.55952380952381</v>
       </c>
     </row>
     <row r="56" spans="1:4">
-      <c r="A56" s="3" t="s">
+      <c r="A56" s="5" t="s">
         <v>58</v>
       </c>
       <c r="B56" s="6">
-        <v>98</v>
+        <v>29</v>
       </c>
       <c r="C56" s="6">
-        <v>35.5</v>
+        <v>5.8</v>
       </c>
       <c r="D56" s="7">
-        <f>(B56-C56)/B56</f>
-        <v>0.637755102040816</v>
+        <f t="shared" si="2"/>
+        <v>0.8</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2127,88 +2117,72 @@
         <v>59</v>
       </c>
       <c r="B57" s="6">
-        <v>168</v>
+        <v>56</v>
       </c>
       <c r="C57" s="6">
-        <v>74</v>
+        <v>22.18</v>
       </c>
       <c r="D57" s="7">
-        <f>(B57-C57)/B57</f>
-        <v>0.55952380952381</v>
+        <f t="shared" si="2"/>
+        <v>0.603928571428571</v>
       </c>
     </row>
     <row r="58" spans="1:4">
-      <c r="A58" s="5" t="s">
+      <c r="A58" s="3" t="s">
         <v>60</v>
       </c>
       <c r="B58" s="6">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="C58" s="6">
-        <v>5.8</v>
+        <v>4</v>
       </c>
       <c r="D58" s="7">
-        <f>(B58-C58)/B58</f>
-        <v>0.8</v>
+        <f t="shared" si="2"/>
+        <v>0.777777777777778</v>
       </c>
     </row>
     <row r="59" spans="1:4">
-      <c r="A59" s="5" t="s">
+      <c r="A59" s="3" t="s">
         <v>61</v>
       </c>
       <c r="B59" s="6">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="C59" s="6">
-        <v>22.18</v>
-      </c>
-      <c r="D59" s="7">
-        <f>(B59-C59)/B59</f>
-        <v>0.603928571428571</v>
+        <v>7.4</v>
+      </c>
+      <c r="D59" s="9">
+        <v>0.735714285714286</v>
       </c>
     </row>
     <row r="60" spans="1:4">
-      <c r="A60" s="8" t="s">
+      <c r="A60" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B60" s="6">
-        <v>18</v>
-      </c>
-      <c r="C60" s="6">
-        <v>4</v>
-      </c>
-      <c r="D60" s="7">
-        <f>(B60-C60)/B60</f>
-        <v>0.777777777777778</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4">
-      <c r="A61" s="12" t="s">
+      <c r="B60" s="2">
+        <v>100</v>
+      </c>
+      <c r="C60" s="2">
+        <v>98</v>
+      </c>
+      <c r="D60" s="10">
+        <f>C60/B60</f>
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B61" s="13">
-        <v>28</v>
-      </c>
-      <c r="C61" s="13">
-        <v>7.4</v>
-      </c>
-      <c r="D61" s="14">
-        <v>0.735714285714286</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4">
-      <c r="A62" s="1" t="s">
+      <c r="B61" s="2">
+        <v>69</v>
+      </c>
+      <c r="C61" s="2">
+        <v>59</v>
+      </c>
+      <c r="E61" s="2" t="s">
         <v>64</v>
-      </c>
-      <c r="B62" s="2">
-        <v>100</v>
-      </c>
-      <c r="C62" s="2">
-        <v>98</v>
-      </c>
-      <c r="D62" s="15">
-        <f>C62/B62</f>
-        <v>0.98</v>
       </c>
     </row>
   </sheetData>
